--- a/Communication/rover_fmeca.xlsx
+++ b/Communication/rover_fmeca.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr autoCompressPictures="0" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mokka\Desktop\Thesis\Communication\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1907027D-EFCF-456E-B6D9-8B2143FA65B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FBB85C6-FC34-46E1-B7F7-CE7F8C55CD72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3276" yWindow="1200" windowWidth="17280" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -1998,9 +1998,6 @@
     <t>Nonzero cmd, zero current and velocity --&gt; DEGRADED mode</t>
   </si>
   <si>
-    <t>High current, low velocity --&gt; DEGRADED mode</t>
-  </si>
-  <si>
     <t>High current, zero velocity --&gt; ESTOP</t>
   </si>
   <si>
@@ -2147,6 +2144,9 @@
   </si>
   <si>
     <t>CN</t>
+  </si>
+  <si>
+    <t>High current, low velocity --&gt; SAFE mode</t>
   </si>
 </sst>
 </file>
@@ -2460,6 +2460,18 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2504,18 +2516,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2845,67 +2845,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="31.8" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="40"/>
-      <c r="M1" s="40"/>
-      <c r="N1" s="40"/>
-      <c r="O1" s="40"/>
-      <c r="P1" s="41"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="44"/>
+      <c r="K1" s="44"/>
+      <c r="L1" s="44"/>
+      <c r="M1" s="44"/>
+      <c r="N1" s="44"/>
+      <c r="O1" s="44"/>
+      <c r="P1" s="45"/>
       <c r="Q1" s="2"/>
-      <c r="U1" s="28" t="s">
+      <c r="U1" s="32" t="s">
         <v>614</v>
       </c>
-      <c r="V1" s="29"/>
-      <c r="W1" s="30"/>
-      <c r="Y1" s="31" t="s">
-        <v>669</v>
-      </c>
-      <c r="Z1" s="32"/>
-      <c r="AB1" s="45" t="s">
-        <v>674</v>
-      </c>
-      <c r="AC1" s="46" t="s">
+      <c r="V1" s="33"/>
+      <c r="W1" s="34"/>
+      <c r="Y1" s="35" t="s">
+        <v>668</v>
+      </c>
+      <c r="Z1" s="36"/>
+      <c r="AB1" s="30" t="s">
         <v>673</v>
       </c>
+      <c r="AC1" s="31" t="s">
+        <v>672</v>
+      </c>
     </row>
     <row r="2" spans="1:29" ht="30.6" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="38" t="s">
+        <v>663</v>
+      </c>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="40" t="s">
+        <v>665</v>
+      </c>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="38" t="s">
         <v>664</v>
       </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="36" t="s">
+      <c r="J2" s="39"/>
+      <c r="K2" s="39"/>
+      <c r="L2" s="39"/>
+      <c r="M2" s="39"/>
+      <c r="N2" s="46"/>
+      <c r="O2" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="P2" s="3" t="s">
         <v>666</v>
-      </c>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="34" t="s">
-        <v>665</v>
-      </c>
-      <c r="J2" s="35"/>
-      <c r="K2" s="35"/>
-      <c r="L2" s="35"/>
-      <c r="M2" s="35"/>
-      <c r="N2" s="42"/>
-      <c r="O2" s="3" t="s">
-        <v>671</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>667</v>
       </c>
       <c r="Q2"/>
       <c r="U2" s="24" t="s">
@@ -2923,12 +2923,12 @@
       <c r="Z2" s="26" t="s">
         <v>619</v>
       </c>
-      <c r="AB2" s="43" cm="1">
+      <c r="AB2" s="28" cm="1">
         <f t="array" ref="AB2:AB8">_xlfn.UNIQUE($M$4:$M$69)</f>
         <v>12</v>
       </c>
-      <c r="AC2" s="44">
-        <f>COUNTIF($M$4:$M$69, AB2)</f>
+      <c r="AC2" s="29">
+        <f t="shared" ref="AC2:AC8" si="0">COUNTIF($M$4:$M$69, AB2)</f>
         <v>6</v>
       </c>
     </row>
@@ -2997,11 +2997,11 @@
       <c r="Z3" s="26" t="s">
         <v>620</v>
       </c>
-      <c r="AB3" s="43">
+      <c r="AB3" s="28">
         <v>9</v>
       </c>
-      <c r="AC3" s="44">
-        <f>COUNTIF($M$4:$M$69, AB3)</f>
+      <c r="AC3" s="29">
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
     </row>
@@ -3071,11 +3071,11 @@
       <c r="Z4" s="26" t="s">
         <v>621</v>
       </c>
-      <c r="AB4" s="43">
+      <c r="AB4" s="28">
         <v>8</v>
       </c>
-      <c r="AC4" s="44">
-        <f>COUNTIF($M$4:$M$69, AB4)</f>
+      <c r="AC4" s="29">
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
     </row>
@@ -3117,7 +3117,7 @@
         <v>4</v>
       </c>
       <c r="M5" s="14">
-        <f t="shared" ref="M5:M68" si="0">K5*L5</f>
+        <f t="shared" ref="M5:M68" si="1">K5*L5</f>
         <v>12</v>
       </c>
       <c r="N5" s="14" t="s">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="Q5"/>
       <c r="U5" s="24" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="V5" s="24">
         <v>1</v>
@@ -3145,11 +3145,11 @@
       <c r="Z5" s="26" t="s">
         <v>622</v>
       </c>
-      <c r="AB5" s="43">
+      <c r="AB5" s="28">
         <v>6</v>
       </c>
-      <c r="AC5" s="44">
-        <f>COUNTIF($M$4:$M$69, AB5)</f>
+      <c r="AC5" s="29">
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
     </row>
@@ -3191,7 +3191,7 @@
         <v>3</v>
       </c>
       <c r="M6" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="N6" s="14" t="s">
@@ -3204,12 +3204,12 @@
         <v>628</v>
       </c>
       <c r="Q6"/>
-      <c r="U6" s="33" t="s">
-        <v>670</v>
-      </c>
-      <c r="V6" s="33"/>
+      <c r="U6" s="37" t="s">
+        <v>669</v>
+      </c>
+      <c r="V6" s="37"/>
       <c r="W6" s="27" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="Y6" s="24">
         <v>5</v>
@@ -3217,11 +3217,11 @@
       <c r="Z6" s="26" t="s">
         <v>623</v>
       </c>
-      <c r="AB6" s="43">
+      <c r="AB6" s="28">
         <v>10</v>
       </c>
-      <c r="AC6" s="44">
-        <f>COUNTIF($M$4:$M$69, AB6)</f>
+      <c r="AC6" s="29">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
         <v>4</v>
       </c>
       <c r="M7" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="N7" s="11" t="s">
@@ -3276,11 +3276,11 @@
         <v>633</v>
       </c>
       <c r="Q7"/>
-      <c r="AB7" s="43">
+      <c r="AB7" s="28">
         <v>4</v>
       </c>
-      <c r="AC7" s="44">
-        <f>COUNTIF($M$4:$M$69, AB7)</f>
+      <c r="AC7" s="29">
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
@@ -3322,7 +3322,7 @@
         <v>4</v>
       </c>
       <c r="M8" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="N8" s="15" t="s">
@@ -3333,11 +3333,11 @@
       </c>
       <c r="P8" s="9"/>
       <c r="Q8"/>
-      <c r="AB8" s="43">
+      <c r="AB8" s="28">
         <v>3</v>
       </c>
-      <c r="AC8" s="44">
-        <f>COUNTIF($M$4:$M$69, AB8)</f>
+      <c r="AC8" s="29">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -3379,7 +3379,7 @@
         <v>2</v>
       </c>
       <c r="M9" s="16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="N9" s="16" t="s">
@@ -3431,7 +3431,7 @@
         <v>4</v>
       </c>
       <c r="M10" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="N10" s="14" t="s">
@@ -3483,7 +3483,7 @@
         <v>3</v>
       </c>
       <c r="M11" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="N11" s="14" t="s">
@@ -3535,7 +3535,7 @@
         <v>3</v>
       </c>
       <c r="M12" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="N12" s="15" t="s">
@@ -3587,7 +3587,7 @@
         <v>4</v>
       </c>
       <c r="M13" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="N13" s="15" t="s">
@@ -3639,7 +3639,7 @@
         <v>4</v>
       </c>
       <c r="M14" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="N14" s="14" t="s">
@@ -3691,7 +3691,7 @@
         <v>3</v>
       </c>
       <c r="M15" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="N15" s="14" t="s">
@@ -3743,7 +3743,7 @@
         <v>2</v>
       </c>
       <c r="M16" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="N16" s="14" t="s">
@@ -3794,7 +3794,7 @@
         <v>2</v>
       </c>
       <c r="M17" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="N17" s="11" t="s">
@@ -3845,7 +3845,7 @@
         <v>4</v>
       </c>
       <c r="M18" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="N18" s="14" t="s">
@@ -3896,7 +3896,7 @@
         <v>3</v>
       </c>
       <c r="M19" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="N19" s="15" t="s">
@@ -3945,7 +3945,7 @@
         <v>5</v>
       </c>
       <c r="M20" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="N20" s="11" t="s">
@@ -3996,7 +3996,7 @@
         <v>3</v>
       </c>
       <c r="M21" s="16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="N21" s="16" t="s">
@@ -4047,7 +4047,7 @@
         <v>4</v>
       </c>
       <c r="M22" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="N22" s="11" t="s">
@@ -4098,7 +4098,7 @@
         <v>2</v>
       </c>
       <c r="M23" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="N23" s="14" t="s">
@@ -4149,7 +4149,7 @@
         <v>1</v>
       </c>
       <c r="M24" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="N24" s="11" t="s">
@@ -4200,7 +4200,7 @@
         <v>3</v>
       </c>
       <c r="M25" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="N25" s="14" t="s">
@@ -4251,7 +4251,7 @@
         <v>2</v>
       </c>
       <c r="M26" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="N26" s="14" t="s">
@@ -4302,7 +4302,7 @@
         <v>2</v>
       </c>
       <c r="M27" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="N27" s="14" t="s">
@@ -4353,7 +4353,7 @@
         <v>2</v>
       </c>
       <c r="M28" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="N28" s="15" t="s">
@@ -4363,7 +4363,7 @@
         <v>242</v>
       </c>
       <c r="P28" s="9" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="29" spans="1:16" ht="75" x14ac:dyDescent="0.25">
@@ -4404,7 +4404,7 @@
         <v>4</v>
       </c>
       <c r="M29" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="N29" s="15" t="s">
@@ -4414,7 +4414,7 @@
         <v>128</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="30" spans="1:16" ht="75" x14ac:dyDescent="0.25">
@@ -4455,7 +4455,7 @@
         <v>3</v>
       </c>
       <c r="M30" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="N30" s="15" t="s">
@@ -4465,7 +4465,7 @@
         <v>258</v>
       </c>
       <c r="P30" s="9" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="31" spans="1:16" ht="90" x14ac:dyDescent="0.25">
@@ -4506,7 +4506,7 @@
         <v>4</v>
       </c>
       <c r="M31" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="N31" s="15" t="s">
@@ -4516,7 +4516,7 @@
         <v>266</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="32" spans="1:16" ht="105" x14ac:dyDescent="0.25">
@@ -4557,7 +4557,7 @@
         <v>2</v>
       </c>
       <c r="M32" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="N32" s="15" t="s">
@@ -4606,7 +4606,7 @@
         <v>2</v>
       </c>
       <c r="M33" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="N33" s="14" t="s">
@@ -4657,7 +4657,7 @@
         <v>1</v>
       </c>
       <c r="M34" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="N34" s="14" t="s">
@@ -4667,7 +4667,7 @@
         <v>293</v>
       </c>
       <c r="P34" s="7" t="s">
-        <v>646</v>
+        <v>674</v>
       </c>
     </row>
     <row r="35" spans="1:16" ht="75" x14ac:dyDescent="0.25">
@@ -4708,7 +4708,7 @@
         <v>2</v>
       </c>
       <c r="M35" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="N35" s="14" t="s">
@@ -4718,7 +4718,7 @@
         <v>301</v>
       </c>
       <c r="P35" s="7" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="36" spans="1:16" ht="90" x14ac:dyDescent="0.25">
@@ -4759,7 +4759,7 @@
         <v>4</v>
       </c>
       <c r="M36" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="N36" s="15" t="s">
@@ -4808,7 +4808,7 @@
         <v>1</v>
       </c>
       <c r="M37" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="N37" s="14" t="s">
@@ -4818,7 +4818,7 @@
         <v>316</v>
       </c>
       <c r="P37" s="7" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="38" spans="1:16" ht="90" x14ac:dyDescent="0.25">
@@ -4859,7 +4859,7 @@
         <v>2</v>
       </c>
       <c r="M38" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="N38" s="11" t="s">
@@ -4869,7 +4869,7 @@
         <v>326</v>
       </c>
       <c r="P38" s="8" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="39" spans="1:16" ht="90" x14ac:dyDescent="0.25">
@@ -4910,7 +4910,7 @@
         <v>3</v>
       </c>
       <c r="M39" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="N39" s="14" t="s">
@@ -4920,7 +4920,7 @@
         <v>335</v>
       </c>
       <c r="P39" s="7" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="40" spans="1:16" ht="105" x14ac:dyDescent="0.25">
@@ -4961,7 +4961,7 @@
         <v>4</v>
       </c>
       <c r="M40" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="N40" s="15" t="s">
@@ -5010,7 +5010,7 @@
         <v>2</v>
       </c>
       <c r="M41" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="N41" s="14" t="s">
@@ -5020,7 +5020,7 @@
         <v>354</v>
       </c>
       <c r="P41" s="7" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="42" spans="1:16" ht="60" x14ac:dyDescent="0.25">
@@ -5061,7 +5061,7 @@
         <v>2</v>
       </c>
       <c r="M42" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="N42" s="14" t="s">
@@ -5071,7 +5071,7 @@
         <v>363</v>
       </c>
       <c r="P42" s="7" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="43" spans="1:16" ht="90" x14ac:dyDescent="0.25">
@@ -5112,7 +5112,7 @@
         <v>2</v>
       </c>
       <c r="M43" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="N43" s="14" t="s">
@@ -5120,7 +5120,7 @@
       </c>
       <c r="O43" s="17"/>
       <c r="P43" s="7" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="44" spans="1:16" ht="75" x14ac:dyDescent="0.25">
@@ -5161,7 +5161,7 @@
         <v>4</v>
       </c>
       <c r="M44" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="N44" s="14" t="s">
@@ -5171,7 +5171,7 @@
         <v>382</v>
       </c>
       <c r="P44" s="7" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="45" spans="1:16" ht="90" x14ac:dyDescent="0.25">
@@ -5212,7 +5212,7 @@
         <v>4</v>
       </c>
       <c r="M45" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="N45" s="15" t="s">
@@ -5222,7 +5222,7 @@
         <v>390</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="46" spans="1:16" ht="75" x14ac:dyDescent="0.25">
@@ -5263,7 +5263,7 @@
         <v>4</v>
       </c>
       <c r="M46" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="N46" s="15" t="s">
@@ -5273,7 +5273,7 @@
         <v>398</v>
       </c>
       <c r="P46" s="9" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="47" spans="1:16" ht="75" x14ac:dyDescent="0.25">
@@ -5314,7 +5314,7 @@
         <v>3</v>
       </c>
       <c r="M47" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="N47" s="14" t="s">
@@ -5324,7 +5324,7 @@
         <v>408</v>
       </c>
       <c r="P47" s="7" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="48" spans="1:16" ht="75" x14ac:dyDescent="0.25">
@@ -5365,7 +5365,7 @@
         <v>3</v>
       </c>
       <c r="M48" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="N48" s="14" t="s">
@@ -5375,7 +5375,7 @@
         <v>408</v>
       </c>
       <c r="P48" s="7" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="49" spans="1:16" ht="75" x14ac:dyDescent="0.25">
@@ -5416,7 +5416,7 @@
         <v>4</v>
       </c>
       <c r="M49" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="N49" s="14" t="s">
@@ -5465,7 +5465,7 @@
         <v>3</v>
       </c>
       <c r="M50" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="N50" s="15" t="s">
@@ -5514,7 +5514,7 @@
         <v>2</v>
       </c>
       <c r="M51" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="N51" s="15" t="s">
@@ -5563,7 +5563,7 @@
         <v>4</v>
       </c>
       <c r="M52" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="N52" s="15" t="s">
@@ -5612,7 +5612,7 @@
         <v>3</v>
       </c>
       <c r="M53" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="N53" s="15" t="s">
@@ -5661,7 +5661,7 @@
         <v>4</v>
       </c>
       <c r="M54" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="N54" s="15" t="s">
@@ -5710,7 +5710,7 @@
         <v>2</v>
       </c>
       <c r="M55" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="N55" s="15" t="s">
@@ -5759,7 +5759,7 @@
         <v>3</v>
       </c>
       <c r="M56" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="N56" s="15" t="s">
@@ -5769,7 +5769,7 @@
         <v>494</v>
       </c>
       <c r="P56" s="9" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="57" spans="1:16" ht="75" x14ac:dyDescent="0.25">
@@ -5810,7 +5810,7 @@
         <v>3</v>
       </c>
       <c r="M57" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="N57" s="15" t="s">
@@ -5820,7 +5820,7 @@
         <v>503</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="58" spans="1:16" ht="90" x14ac:dyDescent="0.25">
@@ -5861,7 +5861,7 @@
         <v>4</v>
       </c>
       <c r="M58" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="N58" s="15" t="s">
@@ -5871,7 +5871,7 @@
         <v>513</v>
       </c>
       <c r="P58" s="9" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="59" spans="1:16" ht="60" x14ac:dyDescent="0.25">
@@ -5912,7 +5912,7 @@
         <v>4</v>
       </c>
       <c r="M59" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="N59" s="15" t="s">
@@ -5922,7 +5922,7 @@
         <v>521</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="60" spans="1:16" ht="90" x14ac:dyDescent="0.25">
@@ -5963,7 +5963,7 @@
         <v>2</v>
       </c>
       <c r="M60" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="N60" s="14" t="s">
@@ -5973,7 +5973,7 @@
         <v>531</v>
       </c>
       <c r="P60" s="7" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="61" spans="1:16" ht="105" x14ac:dyDescent="0.25">
@@ -6014,7 +6014,7 @@
         <v>3</v>
       </c>
       <c r="M61" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="N61" s="14" t="s">
@@ -6024,7 +6024,7 @@
         <v>531</v>
       </c>
       <c r="P61" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="62" spans="1:16" ht="90" x14ac:dyDescent="0.25">
@@ -6065,7 +6065,7 @@
         <v>3</v>
       </c>
       <c r="M62" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="N62" s="14" t="s">
@@ -6075,7 +6075,7 @@
         <v>549</v>
       </c>
       <c r="P62" s="7" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="63" spans="1:16" ht="75" x14ac:dyDescent="0.25">
@@ -6116,7 +6116,7 @@
         <v>4</v>
       </c>
       <c r="M63" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="N63" s="15" t="s">
@@ -6165,7 +6165,7 @@
         <v>3</v>
       </c>
       <c r="M64" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="N64" s="15" t="s">
@@ -6214,7 +6214,7 @@
         <v>2</v>
       </c>
       <c r="M65" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="N65" s="15" t="s">
@@ -6263,7 +6263,7 @@
         <v>4</v>
       </c>
       <c r="M66" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="N66" s="15" t="s">
@@ -6312,7 +6312,7 @@
         <v>5</v>
       </c>
       <c r="M67" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="N67" s="15" t="s">
@@ -6361,7 +6361,7 @@
         <v>4</v>
       </c>
       <c r="M68" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="N68" s="15" t="s">
@@ -6410,7 +6410,7 @@
         <v>5</v>
       </c>
       <c r="M69" s="18">
-        <f t="shared" ref="M69" si="1">K69*L69</f>
+        <f t="shared" ref="M69" si="2">K69*L69</f>
         <v>10</v>
       </c>
       <c r="N69" s="18" t="s">
